--- a/evaluation/det_gpt_domain.xlsx
+++ b/evaluation/det_gpt_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
     </row>
     <row r="2">
@@ -397,7 +397,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
     </row>
     <row r="5">
@@ -429,7 +429,7 @@
         <v>0.4619497266268455</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.5910591466147023</v>
+        <v>0.709322676755627</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.39758261400899414</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="8">
@@ -461,7 +461,7 @@
         <v>0.9776859672120618</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.9</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
     </row>
     <row r="14">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.5247706422018348</v>
       </c>
     </row>
     <row r="17">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9473684210526316</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.16</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.053333333333333344</v>
+        <v>0.5042786069651741</v>
       </c>
     </row>
     <row r="21">
@@ -669,7 +669,7 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5637254901960784</v>
       </c>
     </row>
     <row r="22">
@@ -685,7 +685,7 @@
         <v>1.0</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.9092063492063491</v>
+        <v>0.9046031746031746</v>
       </c>
     </row>
     <row r="23">
@@ -701,7 +701,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.904718137254902</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +733,7 @@
         <v>1.0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9613095238095238</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/det_gpt_domain.xlsx
+++ b/evaluation/det_gpt_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
     </row>
     <row r="2">
@@ -397,7 +397,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -429,7 +429,7 @@
         <v>0.4619497266268455</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.709322676755627</v>
+        <v>0.4891523971983743</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.39758261400899414</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.32407407407407407</v>
       </c>
     </row>
     <row r="8">
@@ -461,7 +461,7 @@
         <v>0.9776859672120618</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.9</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="14">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.5247706422018348</v>
+        <v>0.2697247706422018</v>
       </c>
     </row>
     <row r="17">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.16</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.5042786069651741</v>
+        <v>0.05094527363184081</v>
       </c>
     </row>
     <row r="21">
@@ -669,7 +669,7 @@
         <v>0.4</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="22">
@@ -685,7 +685,7 @@
         <v>1.0</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.9046031746031746</v>
+        <v>0.8182857142857143</v>
       </c>
     </row>
     <row r="23">
@@ -701,7 +701,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +733,7 @@
         <v>1.0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
   </sheetData>
